--- a/runs/20261025-195147-f17d59ed-c79fa2/results.xlsx
+++ b/runs/20261025-195147-f17d59ed-c79fa2/results.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'首次有效结果'!$A$1:$AC$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'全部尝试'!$A$1:$AC$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'全部尝试'!$A$1:$AC$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>2026-10-26T02:33:37.717641+00:00</t>
+          <t>2026-10-26T07:56:53.346298+00:00</t>
         </is>
       </c>
     </row>
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HALTED</t>
+          <t>STOPPED</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"PASSED": 7, "EXECUTION_FAILED": 11, "TIMEOUT": 6, "ENVIRONMENT_ERROR": 22, "TASK_FAILED": 8, "PREFLIGHT_ERROR": 3, "INTERRUPTED": 1, "VERIFIER_ERROR": 1, "PENDING": 28}</t>
+          <t>{"PASSED": 7, "EXECUTION_FAILED": 14, "TIMEOUT": 8, "ENVIRONMENT_ERROR": 38, "TASK_FAILED": 10, "PREFLIGHT_ERROR": 3, "INTERRUPTED": 4, "VERIFIER_ERROR": 1, "PENDING": 2}</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.367816091954023</v>
+        <v>0.4482758620689655</v>
       </c>
     </row>
     <row r="13">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C61" s="2" t="n"/>
@@ -6566,29 +6566,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n"/>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="I61" s="2" t="n">
+        <v>2444.516</v>
+      </c>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
       <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
-      <c r="Q61" s="2" t="n"/>
-      <c r="R61" s="2" t="n"/>
-      <c r="S61" s="2" t="n"/>
-      <c r="T61" s="2" t="n"/>
-      <c r="U61" s="2" t="n"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:8fb3108cfe4365a33fe0', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\pdf-excel-diff\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V61" s="2" t="n"/>
       <c r="W61" s="2" t="n"/>
       <c r="X61" s="2" t="n"/>
       <c r="Y61" s="2" t="n"/>
       <c r="Z61" s="2" t="n"/>
-      <c r="AA61" s="2" t="n"/>
-      <c r="AB61" s="2" t="n"/>
-      <c r="AC61" s="2" t="n"/>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pdf-excel-diff\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6598,7 +6618,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C62" s="2" t="n"/>
@@ -6613,29 +6633,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n"/>
+      <c r="G62" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="I62" s="2" t="n">
+        <v>1800.563</v>
+      </c>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="n"/>
-      <c r="R62" s="2" t="n"/>
-      <c r="S62" s="2" t="n"/>
-      <c r="T62" s="2" t="n"/>
-      <c r="U62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:8003fb7d912e2224836d', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\powerlifting-coef-calc\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V62" s="2" t="n"/>
       <c r="W62" s="2" t="n"/>
       <c r="X62" s="2" t="n"/>
       <c r="Y62" s="2" t="n"/>
       <c r="Z62" s="2" t="n"/>
-      <c r="AA62" s="2" t="n"/>
-      <c r="AB62" s="2" t="n"/>
-      <c r="AC62" s="2" t="n"/>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\powerlifting-coef-calc\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -6645,11 +6685,15 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n"/>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -6660,29 +6704,75 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="n"/>
-      <c r="Q63" s="2" t="n"/>
-      <c r="R63" s="2" t="n"/>
-      <c r="S63" s="2" t="n"/>
+      <c r="G63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>session-868633eb-0450-4b28-8eee-74f0ec329b1c</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>3578.156</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>500.671</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>810459</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>13281</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr"/>
       <c r="T63" s="2" t="n"/>
-      <c r="U63" s="2" t="n"/>
+      <c r="U63" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V63" s="2" t="n"/>
       <c r="W63" s="2" t="n"/>
       <c r="X63" s="2" t="n"/>
       <c r="Y63" s="2" t="n"/>
       <c r="Z63" s="2" t="n"/>
-      <c r="AA63" s="2" t="n"/>
-      <c r="AB63" s="2" t="n"/>
-      <c r="AC63" s="2" t="n"/>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pptx-reference-formatting\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6692,7 +6782,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C64" s="2" t="n"/>
@@ -6707,29 +6797,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n"/>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
+      <c r="I64" s="2" t="n">
+        <v>2745.547</v>
+      </c>
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="n"/>
-      <c r="R64" s="2" t="n"/>
-      <c r="S64" s="2" t="n"/>
-      <c r="T64" s="2" t="n"/>
-      <c r="U64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:d9cdd873b77b544796c3', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\protein-expression-analysis\\environment']' timed out after 900.0 seconds</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V64" s="2" t="n"/>
       <c r="W64" s="2" t="n"/>
       <c r="X64" s="2" t="n"/>
       <c r="Y64" s="2" t="n"/>
       <c r="Z64" s="2" t="n"/>
-      <c r="AA64" s="2" t="n"/>
-      <c r="AB64" s="2" t="n"/>
-      <c r="AC64" s="2" t="n"/>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\protein-expression-analysis\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6739,7 +6849,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C65" s="2" t="n"/>
@@ -6754,29 +6864,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G65" s="2" t="n"/>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
+      <c r="I65" s="2" t="n">
+        <v>1244.172</v>
+      </c>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="n"/>
-      <c r="R65" s="2" t="n"/>
-      <c r="S65" s="2" t="n"/>
-      <c r="T65" s="2" t="n"/>
-      <c r="U65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:81f676554b93b6d46aef', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\python-scala-translation\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V65" s="2" t="n"/>
       <c r="W65" s="2" t="n"/>
       <c r="X65" s="2" t="n"/>
       <c r="Y65" s="2" t="n"/>
       <c r="Z65" s="2" t="n"/>
-      <c r="AA65" s="2" t="n"/>
-      <c r="AB65" s="2" t="n"/>
-      <c r="AC65" s="2" t="n"/>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\python-scala-translation\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6786,11 +6916,15 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -6801,29 +6935,79 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n"/>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="n"/>
-      <c r="S66" s="2" t="n"/>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>session-de4a62dd-4973-4ea0-b158-39d6fdcfd174</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>11129.688</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>3602.484</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>662937</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>127908</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::test_all_files_exist; test_outputs.py::test_grid_dimensions; test_outputs.py::test_values_are_real_and_finite; test_outputs.py::test_csv_sums_to_one; test_outputs.py::test_cases_are_distinct; test_outputs.py::test_wigner_diagonal_sum_matches_reference; test_outputs.py::test_wigner_values_match_reference</t>
+        </is>
+      </c>
       <c r="T66" s="2" t="n"/>
-      <c r="U66" s="2" t="n"/>
+      <c r="U66" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V66" s="2" t="n"/>
       <c r="W66" s="2" t="n"/>
       <c r="X66" s="2" t="n"/>
       <c r="Y66" s="2" t="n"/>
       <c r="Z66" s="2" t="n"/>
-      <c r="AA66" s="2" t="n"/>
-      <c r="AB66" s="2" t="n"/>
-      <c r="AC66" s="2" t="n"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\quantum-numerical-simulation\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6833,11 +7017,15 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -6848,29 +7036,71 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="n"/>
-      <c r="Q67" s="2" t="n"/>
-      <c r="R67" s="2" t="n"/>
-      <c r="S67" s="2" t="n"/>
+      <c r="G67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>session-fc4afe91-74fd-4753-a1c0-b3c45b834253</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>3915.641</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1050.39</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>91732</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>43859</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>finite-horizon-lqr; integral-action-design; mpc-horizon-tuning; state-space-linearization</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>finite-horizon-lqr; integral-action-design; mpc-horizon-tuning; state-space-linearization</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::TestControllerParams::test_controller_params; test_outputs.py::TestControllerParams::test_linearization_correctness; test_outputs.py::TestControlLog::test_control_log; test_outputs.py::TestMetrics::test_metrics; test_outputs.py::TestPerformance::test_performance; test_outputs.py::TestSafety::test_safety</t>
+        </is>
+      </c>
       <c r="T67" s="2" t="n"/>
-      <c r="U67" s="2" t="n"/>
+      <c r="U67" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V67" s="2" t="n"/>
       <c r="W67" s="2" t="n"/>
       <c r="X67" s="2" t="n"/>
       <c r="Y67" s="2" t="n"/>
       <c r="Z67" s="2" t="n"/>
-      <c r="AA67" s="2" t="n"/>
-      <c r="AB67" s="2" t="n"/>
-      <c r="AC67" s="2" t="n"/>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\r2r-mpc-control\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6880,11 +7110,15 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -6895,29 +7129,75 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="n"/>
-      <c r="R68" s="2" t="n"/>
-      <c r="S68" s="2" t="n"/>
+      <c r="G68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>session-78d77ff2-41d0-42a1-9e68-162d78a07ae3</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>3522.953</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1200.5</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>468582</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>60204</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>radar-signal-processing; radar-vital-signs; vital-sign-extraction</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>radar-signal-processing; radar-vital-signs; vital-sign-extraction</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>radar-vital-signs</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>radar-vital-signs</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr"/>
       <c r="T68" s="2" t="n"/>
-      <c r="U68" s="2" t="n"/>
+      <c r="U68" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V68" s="2" t="n"/>
       <c r="W68" s="2" t="n"/>
       <c r="X68" s="2" t="n"/>
       <c r="Y68" s="2" t="n"/>
       <c r="Z68" s="2" t="n"/>
-      <c r="AA68" s="2" t="n"/>
-      <c r="AB68" s="2" t="n"/>
-      <c r="AC68" s="2" t="n"/>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\radar-vital-signs\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6927,7 +7207,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C69" s="2" t="n"/>
@@ -6942,29 +7222,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G69" s="2" t="n"/>
+      <c r="G69" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
+      <c r="I69" s="2" t="n">
+        <v>1910.922</v>
+      </c>
       <c r="J69" s="2" t="n"/>
       <c r="K69" s="2" t="n"/>
       <c r="L69" s="2" t="n"/>
       <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="n"/>
-      <c r="R69" s="2" t="n"/>
-      <c r="S69" s="2" t="n"/>
-      <c r="T69" s="2" t="n"/>
-      <c r="U69" s="2" t="n"/>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:987dcf47146a00260317', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\react-performance-debugging\\environment']' timed out after 1200.0 seconds</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V69" s="2" t="n"/>
       <c r="W69" s="2" t="n"/>
       <c r="X69" s="2" t="n"/>
       <c r="Y69" s="2" t="n"/>
       <c r="Z69" s="2" t="n"/>
-      <c r="AA69" s="2" t="n"/>
-      <c r="AB69" s="2" t="n"/>
-      <c r="AC69" s="2" t="n"/>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\react-performance-debugging\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6974,7 +7274,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C70" s="2" t="n"/>
@@ -6989,29 +7289,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G70" s="2" t="n"/>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
+      <c r="I70" s="2" t="n">
+        <v>601.9059999999999</v>
+      </c>
       <c r="J70" s="2" t="n"/>
       <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
-      <c r="Q70" s="2" t="n"/>
-      <c r="R70" s="2" t="n"/>
-      <c r="S70" s="2" t="n"/>
-      <c r="T70" s="2" t="n"/>
-      <c r="U70" s="2" t="n"/>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:04455a0338c84a104ced', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\reserves-at-risk-calc\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V70" s="2" t="n"/>
       <c r="W70" s="2" t="n"/>
       <c r="X70" s="2" t="n"/>
       <c r="Y70" s="2" t="n"/>
       <c r="Z70" s="2" t="n"/>
-      <c r="AA70" s="2" t="n"/>
-      <c r="AB70" s="2" t="n"/>
-      <c r="AC70" s="2" t="n"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\reserves-at-risk-calc\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -7021,11 +7341,15 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n"/>
+          <t>TASK_FAILED</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -7036,29 +7360,79 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G71" s="2" t="n"/>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
-      <c r="Q71" s="2" t="n"/>
-      <c r="R71" s="2" t="n"/>
-      <c r="S71" s="2" t="n"/>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>session-4e51a62e-4c9a-4307-b094-96bf5123382e</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>600.813</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>413.329</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>448039</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>16141</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>pdf; xlsx</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>pdf; xlsx</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::TestPivotTableConfiguration::test_pivot_row_is_state; test_outputs.py::TestPivotTableConfiguration::test_pivot_uses_correct_aggregation; test_outputs.py::TestSourceDataContent::test_state_values_are_valid; test_outputs.py::TestDataTransformationCorrectness::test_pivot_cache_has_fields</t>
+        </is>
+      </c>
       <c r="T71" s="2" t="n"/>
-      <c r="U71" s="2" t="n"/>
+      <c r="U71" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V71" s="2" t="n"/>
       <c r="W71" s="2" t="n"/>
       <c r="X71" s="2" t="n"/>
       <c r="Y71" s="2" t="n"/>
       <c r="Z71" s="2" t="n"/>
-      <c r="AA71" s="2" t="n"/>
-      <c r="AB71" s="2" t="n"/>
-      <c r="AC71" s="2" t="n"/>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\sales-pivot-analysis\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7068,7 +7442,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C72" s="2" t="n"/>
@@ -7083,29 +7457,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G72" s="2" t="n"/>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
+      <c r="I72" s="2" t="n">
+        <v>600.968</v>
+      </c>
       <c r="J72" s="2" t="n"/>
       <c r="K72" s="2" t="n"/>
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
-      <c r="Q72" s="2" t="n"/>
-      <c r="R72" s="2" t="n"/>
-      <c r="S72" s="2" t="n"/>
-      <c r="T72" s="2" t="n"/>
-      <c r="U72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:db6c1e3425e48d1ab8d1', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\sec-financial-report\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V72" s="2" t="n"/>
       <c r="W72" s="2" t="n"/>
       <c r="X72" s="2" t="n"/>
       <c r="Y72" s="2" t="n"/>
       <c r="Z72" s="2" t="n"/>
-      <c r="AA72" s="2" t="n"/>
-      <c r="AB72" s="2" t="n"/>
-      <c r="AC72" s="2" t="n"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\sec-financial-report\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -7115,7 +7509,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C73" s="2" t="n"/>
@@ -7130,29 +7524,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n"/>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
+      <c r="I73" s="2" t="n">
+        <v>1402.156</v>
+      </c>
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="2" t="n"/>
-      <c r="P73" s="2" t="n"/>
-      <c r="Q73" s="2" t="n"/>
-      <c r="R73" s="2" t="n"/>
-      <c r="S73" s="2" t="n"/>
-      <c r="T73" s="2" t="n"/>
-      <c r="U73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:26e650c9aa2659152a46', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\seismic-phase-picking\\environment']' timed out after 900.0 seconds</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V73" s="2" t="n"/>
       <c r="W73" s="2" t="n"/>
       <c r="X73" s="2" t="n"/>
       <c r="Y73" s="2" t="n"/>
       <c r="Z73" s="2" t="n"/>
-      <c r="AA73" s="2" t="n"/>
-      <c r="AB73" s="2" t="n"/>
-      <c r="AC73" s="2" t="n"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\seismic-phase-picking\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -7162,11 +7576,15 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -7177,29 +7595,79 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
-      <c r="Q74" s="2" t="n"/>
-      <c r="R74" s="2" t="n"/>
-      <c r="S74" s="2" t="n"/>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>session-7d8fe2a3-2c0d-4371-95b0-bb12d56e1316</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>4698.438</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1800.515</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1645428</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>62764</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>test_setup.py::test_discovery</t>
+        </is>
+      </c>
       <c r="T74" s="2" t="n"/>
-      <c r="U74" s="2" t="n"/>
+      <c r="U74" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V74" s="2" t="n"/>
       <c r="W74" s="2" t="n"/>
       <c r="X74" s="2" t="n"/>
       <c r="Y74" s="2" t="n"/>
       <c r="Z74" s="2" t="n"/>
-      <c r="AA74" s="2" t="n"/>
-      <c r="AB74" s="2" t="n"/>
-      <c r="AC74" s="2" t="n"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\setup-fuzzing-py\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7209,7 +7677,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C75" s="2" t="n"/>
@@ -7224,29 +7692,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n"/>
+      <c r="G75" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
+      <c r="I75" s="2" t="n">
+        <v>6610.75</v>
+      </c>
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
       <c r="M75" s="2" t="n"/>
       <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="n"/>
-      <c r="R75" s="2" t="n"/>
-      <c r="S75" s="2" t="n"/>
-      <c r="T75" s="2" t="n"/>
-      <c r="U75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:2cd84b4898a3cf148f01', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\shock-analysis-demand\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V75" s="2" t="n"/>
       <c r="W75" s="2" t="n"/>
       <c r="X75" s="2" t="n"/>
       <c r="Y75" s="2" t="n"/>
       <c r="Z75" s="2" t="n"/>
-      <c r="AA75" s="2" t="n"/>
-      <c r="AB75" s="2" t="n"/>
-      <c r="AC75" s="2" t="n"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\shock-analysis-demand\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -7256,7 +7744,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C76" s="2" t="n"/>
@@ -7271,29 +7759,91 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G76" s="2" t="n"/>
+      <c r="G76" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
+      <c r="I76" s="2" t="n">
+        <v>6004.281</v>
+      </c>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="2" t="n"/>
       <c r="L76" s="2" t="n"/>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="n"/>
-      <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="n"/>
-      <c r="Q76" s="2" t="n"/>
-      <c r="R76" s="2" t="n"/>
-      <c r="S76" s="2" t="n"/>
-      <c r="T76" s="2" t="n"/>
-      <c r="U76" s="2" t="n"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: buntu noble-backports/universe amd64 Packages [31.0 kB]
+#6 212.7 Get:5 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages [15.0 MB]
+#6 218.8 Ign:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 223.8 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 228.8 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 233.9 Ign:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 238.9 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 244.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 249.0 Err:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 249.0   502  Bad Gateway [IP: 91.189.92.23 80]
+#6 254.0 Err:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 254.0   502  Bad Gateway [IP: 91.189.92.23 80]
+#6 259.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 259.0 Reading package lists...
+#6 259.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+#6 259.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/5] RUN apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+238.9 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+244.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+249.0 Err:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+249.0   502  Bad Gateway [IP: 91.189.92.23 80]
+254.0 Err:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+254.0   502  Bad Gateway [IP: 91.189.92.23 80]
+259.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+259.0 Reading package lists...
+259.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+259.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Python, pip, LibreOffice for Excel formula evaluation
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     python3 \
+   8 | &gt;&gt;&gt;     python3-pip \
+   9 | &gt;&gt;&gt;     python3-venv \
+  10 | &gt;&gt;&gt;     libreoffice \
+  11 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  12 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V76" s="2" t="n"/>
       <c r="W76" s="2" t="n"/>
       <c r="X76" s="2" t="n"/>
       <c r="Y76" s="2" t="n"/>
       <c r="Z76" s="2" t="n"/>
-      <c r="AA76" s="2" t="n"/>
-      <c r="AB76" s="2" t="n"/>
-      <c r="AC76" s="2" t="n"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\shock-analysis-supply\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7303,11 +7853,15 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
+          <t>TASK_FAILED</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -7318,29 +7872,71 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n"/>
-      <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="n"/>
-      <c r="R77" s="2" t="n"/>
-      <c r="S77" s="2" t="n"/>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>session-499d97ce-ef84-41d1-ae65-19097119b673</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1544.578</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1323.781</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>1657073</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>40062</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment; pdf</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment; pdf</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
       <c r="T77" s="2" t="n"/>
-      <c r="U77" s="2" t="n"/>
+      <c r="U77" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V77" s="2" t="n"/>
       <c r="W77" s="2" t="n"/>
       <c r="X77" s="2" t="n"/>
       <c r="Y77" s="2" t="n"/>
       <c r="Z77" s="2" t="n"/>
-      <c r="AA77" s="2" t="n"/>
-      <c r="AB77" s="2" t="n"/>
-      <c r="AC77" s="2" t="n"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\simpo-code-reproduction\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7350,7 +7946,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C78" s="2" t="n"/>
@@ -7365,29 +7961,93 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G78" s="2" t="n"/>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="I78" s="2" t="n">
+        <v>861.907</v>
+      </c>
       <c r="J78" s="2" t="n"/>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
       <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="n"/>
-      <c r="O78" s="2" t="n"/>
-      <c r="P78" s="2" t="n"/>
-      <c r="Q78" s="2" t="n"/>
-      <c r="R78" s="2" t="n"/>
-      <c r="S78" s="2" t="n"/>
-      <c r="T78" s="2" t="n"/>
-      <c r="U78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: /debian trixie InRelease
+#6 5.316   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 7.991 Get:2 http://deb.debian.org/debian trixie-updates InRelease [47.3 kB]
+#6 13.00 Err:3 http://deb.debian.org/debian-security trixie-security InRelease
+#6 13.00   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 18.01 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 23.02 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 23.02   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 28.04 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 33.05 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 33.05   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.05 Reading package lists...
+#6 33.06 E: Failed to fetch http://deb.debian.org/debian/dists/trixie/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.06 E: The repository 'http://deb.debian.org/debian trixie InRelease' is no longer signed.
+#6 33.06 E: Failed to fetch http://deb.debian.org/debian-security/dists/trixie-security/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.06 E: The repository 'http://deb.debian.org/debian-security trixie-security InRelease' is no longer signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+23.02 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+23.02   502  Bad Gateway [IP: 199.232.162.132 80]
+28.04 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+33.05 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+33.05   502  Bad Gateway [IP: 199.232.162.132 80]
+33.05 Reading package lists...
+33.06 E: Failed to fetch http://deb.debian.org/debian/dists/trixie/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+33.06 E: The repository 'http://deb.debian.org/debian trixie InRelease' is no longer signed.
+33.06 E: Failed to fetch http://deb.debian.org/debian-security/dists/trixie-security/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+33.06 E: The repository 'http://deb.debian.org/debian-security trixie-security InRelease' is no longer signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install dependencies
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     wget \
+   9 | &gt;&gt;&gt;     gnupg2 \
+  10 | &gt;&gt;&gt;     lsb-release \
+  11 | &gt;&gt;&gt;     git \
+  12 | &gt;&gt;&gt;     unzip \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V78" s="2" t="n"/>
       <c r="W78" s="2" t="n"/>
       <c r="X78" s="2" t="n"/>
       <c r="Y78" s="2" t="n"/>
       <c r="Z78" s="2" t="n"/>
-      <c r="AA78" s="2" t="n"/>
-      <c r="AB78" s="2" t="n"/>
-      <c r="AC78" s="2" t="n"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\software-dependency-audit\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7397,7 +8057,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C79" s="2" t="n"/>
@@ -7412,29 +8072,94 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G79" s="2" t="n"/>
+      <c r="G79" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
+      <c r="I79" s="2" t="n">
+        <v>1085.578</v>
+      </c>
       <c r="J79" s="2" t="n"/>
       <c r="K79" s="2" t="n"/>
       <c r="L79" s="2" t="n"/>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="n"/>
-      <c r="Q79" s="2" t="n"/>
-      <c r="R79" s="2" t="n"/>
-      <c r="S79" s="2" t="n"/>
-      <c r="T79" s="2" t="n"/>
-      <c r="U79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: ges [117 kB]
+#6 160.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 167.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 172.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 172.9   Connection failed [IP: 91.189.92.23 80]
+#6 177.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 182.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 182.9   Connection failed [IP: 91.189.92.23 80]
+#6 187.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 193.0 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 193.0   Connection failed [IP: 91.189.92.23 80]
+#6 193.0 Reading package lists...
+#6 193.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+#6 193.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+#6 193.0 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.92.23 80]
+#6 193.0 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [ 2/11] RUN apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+182.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+182.9   Connection failed [IP: 91.189.92.23 80]
+187.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+193.0 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+193.0   Connection failed [IP: 91.189.92.23 80]
+193.0 Reading package lists...
+193.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+193.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+193.0 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.92.23 80]
+193.0 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+------
+Dockerfile:10
+--------------------
+   9 |     # Install essential packages
+  10 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+  11 | &gt;&gt;&gt;     curl \
+  12 | &gt;&gt;&gt;     wget \
+  13 | &gt;&gt;&gt;     git \
+  14 | &gt;&gt;&gt;     unzip \
+  15 | &gt;&gt;&gt;     zip \
+  16 | &gt;&gt;&gt;     vim \
+  17 | &gt;&gt;&gt;     nano \
+  18 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  19 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V79" s="2" t="n"/>
       <c r="W79" s="2" t="n"/>
       <c r="X79" s="2" t="n"/>
       <c r="Y79" s="2" t="n"/>
       <c r="Z79" s="2" t="n"/>
-      <c r="AA79" s="2" t="n"/>
-      <c r="AB79" s="2" t="n"/>
-      <c r="AC79" s="2" t="n"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\spring-boot-jakarta-migration\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7444,7 +8169,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C80" s="2" t="n"/>
@@ -7459,29 +8184,65 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G80" s="2" t="n"/>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
+      <c r="I80" s="2" t="n">
+        <v>513.75</v>
+      </c>
       <c r="J80" s="2" t="n"/>
       <c r="K80" s="2" t="n"/>
       <c r="L80" s="2" t="n"/>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="n"/>
-      <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
-      <c r="Q80" s="2" t="n"/>
-      <c r="R80" s="2" t="n"/>
-      <c r="S80" s="2" t="n"/>
-      <c r="T80" s="2" t="n"/>
-      <c r="U80" s="2" t="n"/>
+      <c r="O80" s="2" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: #0 building with "desktop-linux" instance using docker driver
+#1 [internal] load build definition from Dockerfile
+#1 transferring dockerfile: 2.45kB done
+#1 DONE 0.0s
+#2 [internal] load metadata for docker.io/jasonish/suricata:7.0.11
+#2 ERROR: failed to do request: Head "https://registry-1.docker.io/v2/jasonish/suricata/manifests/7.0.11": EOF
+------
+ &gt; [internal] load metadata for docker.io/jasonish/suricata:7.0.11:
+------
+Dockerfile:1
+--------------------
+   1 | &gt;&gt;&gt; FROM jasonish/suricata:7.0.11
+   2 |     
+   3 |     ENV DEBIAN_FRONTEND=noninteractive
+--------------------
+ERROR: failed to build: failed to solve: jasonish/suricata:7.0.11: failed to resolve source metadata for docker.io/jasonish/suricata:7.0.11: failed to do request: Head "https://registry-1.docker.io/v2/jasonish/suricata/manifests/7.0.11": EOF
+</t>
+        </is>
+      </c>
+      <c r="U80" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V80" s="2" t="n"/>
       <c r="W80" s="2" t="n"/>
       <c r="X80" s="2" t="n"/>
       <c r="Y80" s="2" t="n"/>
       <c r="Z80" s="2" t="n"/>
-      <c r="AA80" s="2" t="n"/>
-      <c r="AB80" s="2" t="n"/>
-      <c r="AC80" s="2" t="n"/>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\suricata-custom-exfil\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -7491,7 +8252,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>INTERRUPTED</t>
         </is>
       </c>
       <c r="C81" s="2" t="n"/>
@@ -7506,29 +8267,45 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G81" s="2" t="n"/>
+      <c r="G81" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="n"/>
+      <c r="I81" s="2" t="n">
+        <v>1396.984</v>
+      </c>
       <c r="J81" s="2" t="n"/>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
       <c r="M81" s="2" t="n"/>
       <c r="N81" s="2" t="n"/>
-      <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
-      <c r="Q81" s="2" t="n"/>
-      <c r="R81" s="2" t="n"/>
-      <c r="S81" s="2" t="n"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
       <c r="T81" s="2" t="n"/>
-      <c r="U81" s="2" t="n"/>
+      <c r="U81" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V81" s="2" t="n"/>
       <c r="W81" s="2" t="n"/>
       <c r="X81" s="2" t="n"/>
       <c r="Y81" s="2" t="n"/>
       <c r="Z81" s="2" t="n"/>
-      <c r="AA81" s="2" t="n"/>
-      <c r="AB81" s="2" t="n"/>
-      <c r="AC81" s="2" t="n"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\syzkaller-ppdev-syzlang\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7538,7 +8315,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C82" s="2" t="n"/>
@@ -7553,29 +8330,87 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n"/>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="I82" s="2" t="n">
+        <v>296.812</v>
+      </c>
       <c r="J82" s="2" t="n"/>
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="2" t="n"/>
       <c r="N82" s="2" t="n"/>
-      <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
-      <c r="Q82" s="2" t="n"/>
-      <c r="R82" s="2" t="n"/>
-      <c r="S82" s="2" t="n"/>
-      <c r="T82" s="2" t="n"/>
-      <c r="U82" s="2" t="n"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: gn:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+#6 72.77 Err:7 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 72.77   502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.00 Err:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+#6 76.00   502  Bad Gateway [IP: 91.189.92.24 80]
+#6 76.01 Reading package lists...
+#6 76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble InRelease' is not signed.
+#6 76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+70.99 Ign:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+72.77 Err:7 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+72.77   502  Bad Gateway [IP: 91.189.91.82 80]
+76.00 Err:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+76.00   502  Bad Gateway [IP: 91.189.92.24 80]
+76.01 Reading package lists...
+76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble InRelease' is not signed.
+76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Node.js, npm, and Python
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     python3 \
+   9 | &gt;&gt;&gt;     python3-pip \
+  10 | &gt;&gt;&gt;     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash - \
+  11 | &gt;&gt;&gt;     &amp;&amp; apt-get install -y nodejs \
+  12 | &gt;&gt;&gt;     &amp;&amp; apt-get clean \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V82" s="2" t="n"/>
       <c r="W82" s="2" t="n"/>
       <c r="X82" s="2" t="n"/>
       <c r="Y82" s="2" t="n"/>
       <c r="Z82" s="2" t="n"/>
-      <c r="AA82" s="2" t="n"/>
-      <c r="AB82" s="2" t="n"/>
-      <c r="AC82" s="2" t="n"/>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\threejs-structure-parser\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7585,7 +8420,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C83" s="2" t="n"/>
@@ -7600,29 +8435,86 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n"/>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
+      <c r="I83" s="2" t="n">
+        <v>178.062</v>
+      </c>
       <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="n"/>
       <c r="L83" s="2" t="n"/>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n"/>
-      <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
-      <c r="Q83" s="2" t="n"/>
-      <c r="R83" s="2" t="n"/>
-      <c r="S83" s="2" t="n"/>
-      <c r="T83" s="2" t="n"/>
-      <c r="U83" s="2" t="n"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: ntu.com/ubuntu noble/universe amd64 Packages
+#6 73.58 Get:3 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages [45.4 kB]
+#6 74.13 Err:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 74.13   502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.14 Reading package lists...
+#6 74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+#6 74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+68.10 Get:5 http://security.ubuntu.com/ubuntu noble-security/restricted amd64 Packages [1713 kB]
+69.11 Ign:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+73.58 Get:3 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages [45.4 kB]
+74.13 Err:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+74.13   502  Bad Gateway [IP: 91.189.91.82 80]
+74.14 Reading package lists...
+74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Node.js, npm, and Python
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     python3 \
+   9 | &gt;&gt;&gt;     python3-pip \
+  10 | &gt;&gt;&gt;     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash - \
+  11 | &gt;&gt;&gt;     &amp;&amp; apt-get install -y nodejs \
+  12 | &gt;&gt;&gt;     &amp;&amp; apt-get clean \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V83" s="2" t="n"/>
       <c r="W83" s="2" t="n"/>
       <c r="X83" s="2" t="n"/>
       <c r="Y83" s="2" t="n"/>
       <c r="Z83" s="2" t="n"/>
-      <c r="AA83" s="2" t="n"/>
-      <c r="AB83" s="2" t="n"/>
-      <c r="AC83" s="2" t="n"/>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\threejs-to-obj\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7632,7 +8524,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>INTERRUPTED</t>
         </is>
       </c>
       <c r="C84" s="2" t="n"/>
@@ -7647,29 +8539,53 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G84" s="2" t="n"/>
+      <c r="G84" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
+      <c r="I84" s="2" t="n">
+        <v>918.953</v>
+      </c>
       <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n"/>
       <c r="L84" s="2" t="n"/>
       <c r="M84" s="2" t="n"/>
       <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="n"/>
-      <c r="R84" s="2" t="n"/>
-      <c r="S84" s="2" t="n"/>
-      <c r="T84" s="2" t="n"/>
-      <c r="U84" s="2" t="n"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>transaction-concurrency-control-foundations; transaction-protocol-reasoning; transaction-trace-analysis</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>Stop requested</t>
+        </is>
+      </c>
+      <c r="U84" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V84" s="2" t="n"/>
       <c r="W84" s="2" t="n"/>
       <c r="X84" s="2" t="n"/>
       <c r="Y84" s="2" t="n"/>
       <c r="Z84" s="2" t="n"/>
-      <c r="AA84" s="2" t="n"/>
-      <c r="AB84" s="2" t="n"/>
-      <c r="AC84" s="2" t="n"/>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\tictoc-unnecessary-abort-detection\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7679,7 +8595,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>INTERRUPTED</t>
         </is>
       </c>
       <c r="C85" s="2" t="n"/>
@@ -7694,29 +8610,53 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G85" s="2" t="n"/>
+      <c r="G85" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
+      <c r="I85" s="2" t="n">
+        <v>842.812</v>
+      </c>
       <c r="J85" s="2" t="n"/>
       <c r="K85" s="2" t="n"/>
       <c r="L85" s="2" t="n"/>
       <c r="M85" s="2" t="n"/>
       <c r="N85" s="2" t="n"/>
-      <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
-      <c r="Q85" s="2" t="n"/>
-      <c r="R85" s="2" t="n"/>
-      <c r="S85" s="2" t="n"/>
-      <c r="T85" s="2" t="n"/>
-      <c r="U85" s="2" t="n"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>search-accommodations; search-attractions; search-cities; search-driving-distance; search-flights; search-restaurants</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>Stop requested</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="V85" s="2" t="n"/>
       <c r="W85" s="2" t="n"/>
       <c r="X85" s="2" t="n"/>
       <c r="Y85" s="2" t="n"/>
       <c r="Z85" s="2" t="n"/>
-      <c r="AA85" s="2" t="n"/>
-      <c r="AB85" s="2" t="n"/>
-      <c r="AC85" s="2" t="n"/>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\travel-planning\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7726,7 +8666,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
       <c r="C86" s="2" t="n"/>
@@ -7741,29 +8681,49 @@
           <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
         </is>
       </c>
-      <c r="G86" s="2" t="n"/>
+      <c r="G86" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
+      <c r="I86" s="2" t="n">
+        <v>763.078</v>
+      </c>
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n"/>
       <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="n"/>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="n"/>
-      <c r="R86" s="2" t="n"/>
-      <c r="S86" s="2" t="n"/>
-      <c r="T86" s="2" t="n"/>
-      <c r="U86" s="2" t="n"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:61ba44051c2945cb6276', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\video-silence-remover\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="b">
+        <v>0</v>
+      </c>
       <c r="V86" s="2" t="n"/>
       <c r="W86" s="2" t="n"/>
       <c r="X86" s="2" t="n"/>
       <c r="Y86" s="2" t="n"/>
       <c r="Z86" s="2" t="n"/>
-      <c r="AA86" s="2" t="n"/>
-      <c r="AB86" s="2" t="n"/>
-      <c r="AC86" s="2" t="n"/>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\video-silence-remover\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7871,7 +8831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12466,7 +13426,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>lean4-proof</t>
+          <t>latex-formula-extraction</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -12487,11 +13447,11 @@
         </is>
       </c>
       <c r="G48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="n">
-        <v>629.7190000000001</v>
+        <v>1200.281</v>
       </c>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
@@ -12505,33 +13465,25 @@
       <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:43b2d92186582c659aea', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\lean4-proof\\environment']' timed out after 600.0 seconds</t>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:4ea31b0a0ad3ecab963b', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\latex-formula-extraction\\environment']' timed out after 1200.0 seconds</t>
         </is>
       </c>
       <c r="U48" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_INCOMPLETE</t>
-        </is>
-      </c>
+      <c r="V48" s="2" t="n"/>
       <c r="W48" s="2" t="n"/>
       <c r="X48" s="2" t="n"/>
       <c r="Y48" s="2" t="n"/>
-      <c r="Z48" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\lean4-proof\attempt-001\analysis\20261026-103129\report.md</t>
-        </is>
-      </c>
+      <c r="Z48" s="2" t="n"/>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\lean4-proof\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\latex-formula-extraction\attempt-002</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="n">
@@ -12541,20 +13493,16 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>llm-prefix-cache-replay</t>
+          <t>lean4-proof</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="2" t="n">
-        <v>1</v>
-      </c>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -12568,62 +13516,44 @@
       <c r="G49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>session-9ec20710-c64c-4de0-bfbc-4def37da1dcc</t>
-        </is>
-      </c>
+      <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="n">
-        <v>778.625</v>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>108.265</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M49" s="2" t="n">
-        <v>164407</v>
-      </c>
-      <c r="N49" s="2" t="n">
-        <v>3972</v>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>cache-policy-comparison; prefix-cache-replay</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>cache-policy-comparison; prefix-cache-replay</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>prefix-cache-replay</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>prefix-cache-replay</t>
-        </is>
-      </c>
+        <v>629.7190000000001</v>
+      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr"/>
-      <c r="T49" s="2" t="n"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:43b2d92186582c659aea', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\lean4-proof\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
       <c r="U49" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V49" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_INCOMPLETE</t>
+        </is>
+      </c>
       <c r="W49" s="2" t="n"/>
       <c r="X49" s="2" t="n"/>
       <c r="Y49" s="2" t="n"/>
-      <c r="Z49" s="2" t="n"/>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\lean4-proof\attempt-001\analysis\20261026-103129\report.md</t>
+        </is>
+      </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\llm-prefix-cache-replay\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\lean4-proof\attempt-001</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -12638,18 +13568,20 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-codebook-normalization</t>
+          <t>llm-prefix-cache-replay</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>TIMEOUT</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -12665,45 +13597,45 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>session-6c46f920-4ddf-434a-a39c-c3c63b78ddc9</t>
+          <t>session-9ec20710-c64c-4de0-bfbc-4def37da1dcc</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1923.594</v>
+        <v>778.625</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1800.485</v>
+        <v>108.265</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1168203</v>
+        <v>164407</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>94555</v>
+        <v>3972</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-failure-reason-codebook-normalization</t>
+          <t>cache-policy-comparison; prefix-cache-replay</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-failure-reason-codebook-normalization</t>
+          <t>cache-policy-comparison; prefix-cache-replay</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-failure-reason-codebook-normalization</t>
+          <t>prefix-cache-replay</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-failure-reason-codebook-normalization</t>
+          <t>prefix-cache-replay</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr"/>
@@ -12711,22 +13643,14 @@
       <c r="U50" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_INCOMPLETE</t>
-        </is>
-      </c>
+      <c r="V50" s="2" t="n"/>
       <c r="W50" s="2" t="n"/>
       <c r="X50" s="2" t="n"/>
       <c r="Y50" s="2" t="n"/>
-      <c r="Z50" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-codebook-normalization\attempt-001\analysis\20261026-103137\report.md</t>
-        </is>
-      </c>
+      <c r="Z50" s="2" t="n"/>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-codebook-normalization\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\llm-prefix-cache-replay\attempt-001</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -12741,15 +13665,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-equipment-maintenance</t>
+          <t>manufacturing-codebook-normalization</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>VERIFIER_ERROR</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n"/>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -12766,45 +13692,45 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>session-44098adc-b301-4500-9d0a-ca29b6641260</t>
+          <t>session-6c46f920-4ddf-434a-a39c-c3c63b78ddc9</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1194.031</v>
+        <v>1923.594</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1097.141</v>
+        <v>1800.485</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1670109</v>
+        <v>1168203</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>37610</v>
+        <v>94555</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>reflow-machine-maintenance-guidance; reflow-profile-compliance-toolkit</t>
+          <t>manufacturing-failure-reason-codebook-normalization</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>reflow-machine-maintenance-guidance; reflow-profile-compliance-toolkit</t>
+          <t>manufacturing-failure-reason-codebook-normalization</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>reflow-profile-compliance-toolkit</t>
+          <t>manufacturing-failure-reason-codebook-normalization</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>reflow-profile-compliance-toolkit</t>
+          <t>manufacturing-failure-reason-codebook-normalization</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr"/>
@@ -12822,12 +13748,12 @@
       <c r="Y51" s="2" t="n"/>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-equipment-maintenance\attempt-001\analysis\20261026-103146\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-codebook-normalization\attempt-001\analysis\20261026-103137\report.md</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-equipment-maintenance\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-codebook-normalization\attempt-001</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -12842,17 +13768,15 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>manufacturing-fjsp-optimization</t>
+          <t>manufacturing-equipment-maintenance</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>EXECUTION_FAILED</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>VERIFIER_ERROR</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -12869,45 +13793,45 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>session-6ef455aa-2753-4de3-8e43-9563c638897f</t>
+          <t>session-44098adc-b301-4500-9d0a-ca29b6641260</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>734.297</v>
+        <v>1194.031</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>684</v>
+        <v>1097.141</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>41213</v>
+        <v>1670109</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>588</v>
+        <v>37610</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+          <t>reflow-machine-maintenance-guidance; reflow-profile-compliance-toolkit</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+          <t>reflow-machine-maintenance-guidance; reflow-profile-compliance-toolkit</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+          <t>reflow-profile-compliance-toolkit</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+          <t>reflow-profile-compliance-toolkit</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr"/>
@@ -12925,12 +13849,12 @@
       <c r="Y52" s="2" t="n"/>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-fjsp-optimization\attempt-001\analysis\20261026-103157\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-equipment-maintenance\attempt-001\analysis\20261026-103146\report.md</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-fjsp-optimization\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-equipment-maintenance\attempt-001</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -12945,15 +13869,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>mario-coin-counting</t>
+          <t>manufacturing-fjsp-optimization</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>ENVIRONMENT_ERROR</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n"/>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -12968,27 +13894,53 @@
       <c r="G53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>session-6ef455aa-2753-4de3-8e43-9563c638897f</t>
+        </is>
+      </c>
       <c r="I53" s="2" t="n">
-        <v>600.312</v>
-      </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr"/>
-      <c r="Q53" s="2" t="inlineStr"/>
-      <c r="R53" s="2" t="inlineStr"/>
+        <v>734.297</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>684</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>41213</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>fjsp-baseline-repair-with-downtime-and-policy</t>
+        </is>
+      </c>
       <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:19f09df440a8f7b84882', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\mario-coin-counting\\environment']' timed out after 600.0 seconds</t>
-        </is>
-      </c>
+      <c r="T53" s="2" t="n"/>
       <c r="U53" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
@@ -13000,12 +13952,12 @@
       <c r="Y53" s="2" t="n"/>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mario-coin-counting\attempt-001\analysis\20261026-103207\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-fjsp-optimization\attempt-001\analysis\20261026-103157\report.md</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mario-coin-counting\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\manufacturing-fjsp-optimization\attempt-001</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -13020,20 +13972,16 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>mars-clouds-clustering</t>
+          <t>mario-coin-counting</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>EXECUTION_FAILED</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="n">
-        <v>0</v>
-      </c>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
           <t>qwen3.8-27b</t>
@@ -13047,57 +13995,27 @@
       <c r="G54" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>session-dde68ded-5c86-416c-a13a-f86fbb03beea</t>
-        </is>
-      </c>
+      <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="n">
-        <v>1296.453</v>
-      </c>
-      <c r="J54" s="2" t="n">
-        <v>225.531</v>
-      </c>
-      <c r="K54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M54" s="2" t="n">
-        <v>43486</v>
-      </c>
-      <c r="N54" s="2" t="n">
-        <v>1586</v>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>test_outputs.py::TestParetoFrontier::test_result_file_exists; test_outputs.py::TestParetoFrontier::test_result_file_not_empty; test_outputs.py::TestParetoFrontier::test_required_columns; test_outputs.py::TestParetoFrontier::test_f1_values_valid; test_outputs.py::TestParetoFrontier::test_delta_values_positive; test_outputs.py::TestParetoFrontier::test_hyperparameter_ranges; test_outputs.py::TestParetoFrontier::test_is_valid_pareto_frontier; test_outputs.py::TestParetoFrontier::test_all_expected_points_found</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="n"/>
+        <v>600.312</v>
+      </c>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:19f09df440a8f7b84882', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\mario-coin-counting\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
@@ -13109,12 +14027,12 @@
       <c r="Y54" s="2" t="n"/>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mars-clouds-clustering\attempt-001\analysis\20261026-103215\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mario-coin-counting\attempt-001\analysis\20261026-103207\report.md</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mars-clouds-clustering\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mario-coin-counting\attempt-001</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -13129,44 +14047,153 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>mars-clouds-clustering</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>session-dde68ded-5c86-416c-a13a-f86fbb03beea</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>1296.453</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>225.531</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>43486</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>1586</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>custom-distance-metrics; parallel-processing; pareto-optimization</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::TestParetoFrontier::test_result_file_exists; test_outputs.py::TestParetoFrontier::test_result_file_not_empty; test_outputs.py::TestParetoFrontier::test_required_columns; test_outputs.py::TestParetoFrontier::test_f1_values_valid; test_outputs.py::TestParetoFrontier::test_delta_values_positive; test_outputs.py::TestParetoFrontier::test_hyperparameter_ranges; test_outputs.py::TestParetoFrontier::test_is_valid_pareto_frontier; test_outputs.py::TestParetoFrontier::test_all_expected_points_found</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="n"/>
+      <c r="U55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="n"/>
+      <c r="X55" s="2" t="n"/>
+      <c r="Y55" s="2" t="n"/>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mars-clouds-clustering\attempt-001\analysis\20261026-103215\report.md</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\mars-clouds-clustering\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>multilingual-video-dubbing</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n">
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n">
         <v>817.828</v>
       </c>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="inlineStr"/>
-      <c r="P55" s="2" t="inlineStr"/>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr">
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1: ocess "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     python3 python3-pip python3-dev python3-venv     ffmpeg espeak-ng git     libgomp1 libsox-dev sox wget     build-essential cmake     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
 ------
@@ -13197,81 +14224,6 @@
 </t>
         </is>
       </c>
-      <c r="U55" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="n"/>
-      <c r="X55" s="2" t="n"/>
-      <c r="Y55" s="2" t="n"/>
-      <c r="Z55" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\multilingual-video-dubbing\attempt-001\analysis\20261026-103224\report.md</t>
-        </is>
-      </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\multilingual-video-dubbing\attempt-001</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>offer-letter-generator</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>ENVIRONMENT_ERROR</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n">
-        <v>1062.906</v>
-      </c>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="inlineStr"/>
-      <c r="P56" s="2" t="inlineStr"/>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:cb3fd9f64c76605d1d71', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\offer-letter-generator\\environment']' timed out after 600.0 seconds</t>
-        </is>
-      </c>
       <c r="U56" s="2" t="b">
         <v>0</v>
       </c>
@@ -13285,12 +14237,12 @@
       <c r="Y56" s="2" t="n"/>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\offer-letter-generator\attempt-001\analysis\20261026-103233\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\multilingual-video-dubbing\attempt-001\analysis\20261026-103224\report.md</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\offer-letter-generator\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\multilingual-video-dubbing\attempt-001</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -13305,7 +14257,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>organize-messy-files</t>
+          <t>offer-letter-generator</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -13330,7 +14282,7 @@
       </c>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="n">
-        <v>617.125</v>
+        <v>1062.906</v>
       </c>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
@@ -13343,6 +14295,81 @@
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:cb3fd9f64c76605d1d71', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\offer-letter-generator\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="n"/>
+      <c r="X57" s="2" t="n"/>
+      <c r="Y57" s="2" t="n"/>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\offer-letter-generator\attempt-001\analysis\20261026-103233\report.md</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\offer-letter-generator\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>organize-messy-files</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n">
+        <v>617.125</v>
+      </c>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1: 8.0.105 80]
 #6 15.29 Reading package lists...
@@ -13385,77 +14412,77 @@
 </t>
         </is>
       </c>
-      <c r="U57" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="U58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>ANALYSIS_INCOMPLETE</t>
         </is>
       </c>
-      <c r="W57" s="2" t="n"/>
-      <c r="X57" s="2" t="n"/>
-      <c r="Y57" s="2" t="n"/>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="W58" s="2" t="n"/>
+      <c r="X58" s="2" t="n"/>
+      <c r="Y58" s="2" t="n"/>
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\organize-messy-files\attempt-001\analysis\20261026-103241\report.md</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\organize-messy-files\attempt-001</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
+      <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
         </is>
       </c>
-      <c r="AC57" s="2" t="n">
+      <c r="AC58" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>paper-anonymizer</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n">
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n">
         <v>378.985</v>
       </c>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
-      <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="inlineStr"/>
-      <c r="P58" s="2" t="inlineStr"/>
-      <c r="Q58" s="2" t="inlineStr"/>
-      <c r="R58" s="2" t="inlineStr"/>
-      <c r="S58" s="2" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr">
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1:   502  Bad Gateway [IP: 198.18.0.105 80]
 #6 15.19 Reading package lists...
@@ -13498,91 +14525,8 @@
 </t>
         </is>
       </c>
-      <c r="U58" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>ANALYSIS_INCOMPLETE</t>
-        </is>
-      </c>
-      <c r="W58" s="2" t="n"/>
-      <c r="X58" s="2" t="n"/>
-      <c r="Y58" s="2" t="n"/>
-      <c r="Z58" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paper-anonymizer\attempt-001\analysis\20261026-103249\report.md</t>
-        </is>
-      </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paper-anonymizer\attempt-001</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>parallel-tfidf-search</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>PREFLIGHT_ERROR</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n">
-        <v>129.094</v>
-      </c>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
-      <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>memory-optimization; python-parallelization; workload-balancing</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>memory-optimization; python-parallelization; workload-balancing</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr"/>
-      <c r="R59" s="2" t="inlineStr"/>
-      <c r="S59" s="2" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>Framework tool preflight failed: {"status": "REQUEST_FAILED", "payload": {"rootMessageId": "request-d780473d-bda9-40c1-a687-b66485597729", "requestId": "request-d780473d-bda9-40c1-a687-b66485597729", "runId": "run-ce569886-8e7a-4aa2-9098-7544a039f426", "requestContextId": "context-9503b979-325d-417e-b29c-f1b05ff35e2b", "status": "FAILED", "content": "Request failed: Model invocation failed safely.", "text": "Request failed: Model invocation failed safely.", "contentType": "PLAIN_TEXT", "metadata": {"accumulated": true}, "code": "MODEL_PROVIDER_UNAVAILABLE", "message": "The model service is temporarily unavailable. Please retry later.", "category": "UNAVAILABLE", "retryable": false, "hookResults": [{"hookInvocationId": "hook-6f1626c4-8c99-414a-b5f4-1d9057b0b755", "hookId": "user-query-memory-recall", "stage": "BEFORE_MODEL_INVOKE", "status": "SUCCESS", "failureMode": "CONTINUE", "outcome": "PASS"}]}, "sequence": 8}</t>
-        </is>
-      </c>
       <c r="U59" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
@@ -13594,12 +14538,12 @@
       <c r="Y59" s="2" t="n"/>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\parallel-tfidf-search\attempt-001\analysis\20261026-103258\report.md</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paper-anonymizer\attempt-001\analysis\20261026-103249\report.md</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\parallel-tfidf-search\attempt-001</t>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paper-anonymizer\attempt-001</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
@@ -13614,12 +14558,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>paratransit-routing</t>
+          <t>parallel-tfidf-search</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ENVIRONMENT_ERROR</t>
+          <t>PREFLIGHT_ERROR</t>
         </is>
       </c>
       <c r="C60" s="2" t="n"/>
@@ -13639,19 +14583,102 @@
       </c>
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="n">
-        <v>87.922</v>
+        <v>129.094</v>
       </c>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="inlineStr"/>
-      <c r="P60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>memory-optimization; python-parallelization; workload-balancing</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>memory-optimization; python-parallelization; workload-balancing</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="inlineStr"/>
       <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>Framework tool preflight failed: {"status": "REQUEST_FAILED", "payload": {"rootMessageId": "request-d780473d-bda9-40c1-a687-b66485597729", "requestId": "request-d780473d-bda9-40c1-a687-b66485597729", "runId": "run-ce569886-8e7a-4aa2-9098-7544a039f426", "requestContextId": "context-9503b979-325d-417e-b29c-f1b05ff35e2b", "status": "FAILED", "content": "Request failed: Model invocation failed safely.", "text": "Request failed: Model invocation failed safely.", "contentType": "PLAIN_TEXT", "metadata": {"accumulated": true}, "code": "MODEL_PROVIDER_UNAVAILABLE", "message": "The model service is temporarily unavailable. Please retry later.", "category": "UNAVAILABLE", "retryable": false, "hookResults": [{"hookInvocationId": "hook-6f1626c4-8c99-414a-b5f4-1d9057b0b755", "hookId": "user-query-memory-recall", "stage": "BEFORE_MODEL_INVOKE", "status": "SUCCESS", "failureMode": "CONTINUE", "outcome": "PASS"}]}, "sequence": 8}</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>ANALYSIS_INCOMPLETE</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="n"/>
+      <c r="X60" s="2" t="n"/>
+      <c r="Y60" s="2" t="n"/>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\parallel-tfidf-search\attempt-001\analysis\20261026-103258\report.md</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\parallel-tfidf-search\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>paratransit-routing</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n">
+        <v>87.922</v>
+      </c>
+      <c r="J61" s="2" t="n"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
+      <c r="M61" s="2" t="n"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1: rror(8, '[SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in violation of protocol (_ssl.c:1010)'))) - skipping
 #6 38.82 ERROR: Could not find a version that satisfies the requirement ortools==9.11.4210 (from versions: none)
@@ -13683,77 +14710,77 @@
 </t>
         </is>
       </c>
-      <c r="U60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="U61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>ANALYSIS_INCOMPLETE</t>
         </is>
       </c>
-      <c r="W60" s="2" t="n"/>
-      <c r="X60" s="2" t="n"/>
-      <c r="Y60" s="2" t="n"/>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="n"/>
+      <c r="X61" s="2" t="n"/>
+      <c r="Y61" s="2" t="n"/>
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paratransit-routing\attempt-001\analysis\20261026-103307\report.md</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\paratransit-routing\attempt-001</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
+      <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
         </is>
       </c>
-      <c r="AC60" s="2" t="n">
+      <c r="AC61" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>pddl-airport-planning</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n">
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n">
         <v>111.813</v>
       </c>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="inlineStr"/>
-      <c r="P61" s="2" t="inlineStr"/>
-      <c r="Q61" s="2" t="inlineStr"/>
-      <c r="R61" s="2" t="inlineStr"/>
-      <c r="S61" s="2" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr">
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="2" t="n"/>
+      <c r="L62" s="2" t="n"/>
+      <c r="M62" s="2" t="n"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1: ess "/bin/sh -c pip3 install --break-system-packages     requests==2.32.3     bibtexparser==1.4.2     pyyaml==6.0.3     numpy==2.4.1     pyperplan==2.1     unified_planning==1.3.0     up-pyperplan==1.1.0" did not complete successfully: exit code: 1
 ------
@@ -13784,77 +14811,77 @@
 </t>
         </is>
       </c>
-      <c r="U61" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="U62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
         <is>
           <t>ANALYSIS_INCOMPLETE</t>
         </is>
       </c>
-      <c r="W61" s="2" t="n"/>
-      <c r="X61" s="2" t="n"/>
-      <c r="Y61" s="2" t="n"/>
-      <c r="Z61" s="2" t="inlineStr">
+      <c r="W62" s="2" t="n"/>
+      <c r="X62" s="2" t="n"/>
+      <c r="Y62" s="2" t="n"/>
+      <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pddl-airport-planning\attempt-001\analysis\20261026-103315\report.md</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
+      <c r="AA62" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pddl-airport-planning\attempt-001</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
+      <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
         </is>
       </c>
-      <c r="AC61" s="2" t="n">
+      <c r="AC62" s="2" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>pddl-tpp-planning</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>ENVIRONMENT_ERROR</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>qwen3.8-27b</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n">
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n">
         <v>45.532</v>
       </c>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="n"/>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="inlineStr"/>
-      <c r="P62" s="2" t="inlineStr"/>
-      <c r="Q62" s="2" t="inlineStr"/>
-      <c r="R62" s="2" t="inlineStr"/>
-      <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr">
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">docker exited 1: #0 building with "desktop-linux" instance using docker driver
 #1 [internal] load build definition from Dockerfile
@@ -13896,38 +14923,2220 @@
 </t>
         </is>
       </c>
-      <c r="U62" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="U63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>ANALYSIS_INCOMPLETE</t>
         </is>
       </c>
-      <c r="W62" s="2" t="n"/>
-      <c r="X62" s="2" t="n"/>
-      <c r="Y62" s="2" t="n"/>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="n"/>
+      <c r="X63" s="2" t="n"/>
+      <c r="Y63" s="2" t="n"/>
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pddl-tpp-planning\attempt-001\analysis\20261026-103324\report.md</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pddl-tpp-planning\attempt-001</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>4f5d50753f4f23abc988562533a0deb321ea508210f2a493c734457a39d64064</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="n">
+      <c r="AC63" s="2" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>pdf-excel-diff</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n">
+        <v>2444.516</v>
+      </c>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:8fb3108cfe4365a33fe0', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\pdf-excel-diff\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V64" s="2" t="n"/>
+      <c r="W64" s="2" t="n"/>
+      <c r="X64" s="2" t="n"/>
+      <c r="Y64" s="2" t="n"/>
+      <c r="Z64" s="2" t="n"/>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pdf-excel-diff\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>powerlifting-coef-calc</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n">
+        <v>1800.563</v>
+      </c>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:8003fb7d912e2224836d', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\powerlifting-coef-calc\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V65" s="2" t="n"/>
+      <c r="W65" s="2" t="n"/>
+      <c r="X65" s="2" t="n"/>
+      <c r="Y65" s="2" t="n"/>
+      <c r="Z65" s="2" t="n"/>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\powerlifting-coef-calc\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>pptx-reference-formatting</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>session-868633eb-0450-4b28-8eee-74f0ec329b1c</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>3578.156</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>500.671</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>810459</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>13281</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="n"/>
+      <c r="U66" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V66" s="2" t="n"/>
+      <c r="W66" s="2" t="n"/>
+      <c r="X66" s="2" t="n"/>
+      <c r="Y66" s="2" t="n"/>
+      <c r="Z66" s="2" t="n"/>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\pptx-reference-formatting\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>protein-expression-analysis</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n">
+        <v>2745.547</v>
+      </c>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+      <c r="M67" s="2" t="n"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="2" t="inlineStr"/>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:d9cdd873b77b544796c3', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\protein-expression-analysis\\environment']' timed out after 900.0 seconds</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V67" s="2" t="n"/>
+      <c r="W67" s="2" t="n"/>
+      <c r="X67" s="2" t="n"/>
+      <c r="Y67" s="2" t="n"/>
+      <c r="Z67" s="2" t="n"/>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\protein-expression-analysis\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>python-scala-translation</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="n"/>
+      <c r="I68" s="2" t="n">
+        <v>1244.172</v>
+      </c>
+      <c r="J68" s="2" t="n"/>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:81f676554b93b6d46aef', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\python-scala-translation\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V68" s="2" t="n"/>
+      <c r="W68" s="2" t="n"/>
+      <c r="X68" s="2" t="n"/>
+      <c r="Y68" s="2" t="n"/>
+      <c r="Z68" s="2" t="n"/>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\python-scala-translation\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>quantum-numerical-simulation</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>session-de4a62dd-4973-4ea0-b158-39d6fdcfd174</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>11129.688</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>3602.484</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>662937</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>127908</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>qutip</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::test_all_files_exist; test_outputs.py::test_grid_dimensions; test_outputs.py::test_values_are_real_and_finite; test_outputs.py::test_csv_sums_to_one; test_outputs.py::test_cases_are_distinct; test_outputs.py::test_wigner_diagonal_sum_matches_reference; test_outputs.py::test_wigner_values_match_reference</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="n"/>
+      <c r="U69" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V69" s="2" t="n"/>
+      <c r="W69" s="2" t="n"/>
+      <c r="X69" s="2" t="n"/>
+      <c r="Y69" s="2" t="n"/>
+      <c r="Z69" s="2" t="n"/>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\quantum-numerical-simulation\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>r2r-mpc-control</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>EXECUTION_FAILED</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>session-fc4afe91-74fd-4753-a1c0-b3c45b834253</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>3915.641</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1050.39</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>91732</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>43859</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>finite-horizon-lqr; integral-action-design; mpc-horizon-tuning; state-space-linearization</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>finite-horizon-lqr; integral-action-design; mpc-horizon-tuning; state-space-linearization</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::TestControllerParams::test_controller_params; test_outputs.py::TestControllerParams::test_linearization_correctness; test_outputs.py::TestControlLog::test_control_log; test_outputs.py::TestMetrics::test_metrics; test_outputs.py::TestPerformance::test_performance; test_outputs.py::TestSafety::test_safety</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n"/>
+      <c r="U70" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V70" s="2" t="n"/>
+      <c r="W70" s="2" t="n"/>
+      <c r="X70" s="2" t="n"/>
+      <c r="Y70" s="2" t="n"/>
+      <c r="Z70" s="2" t="n"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\r2r-mpc-control\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>radar-vital-signs</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>session-78d77ff2-41d0-42a1-9e68-162d78a07ae3</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>3522.953</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1200.5</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>468582</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>60204</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>radar-signal-processing; radar-vital-signs; vital-sign-extraction</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>radar-signal-processing; radar-vital-signs; vital-sign-extraction</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>radar-vital-signs</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>radar-vital-signs</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="n"/>
+      <c r="U71" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V71" s="2" t="n"/>
+      <c r="W71" s="2" t="n"/>
+      <c r="X71" s="2" t="n"/>
+      <c r="Y71" s="2" t="n"/>
+      <c r="Z71" s="2" t="n"/>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\radar-vital-signs\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>react-performance-debugging</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n">
+        <v>1910.922</v>
+      </c>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:987dcf47146a00260317', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\react-performance-debugging\\environment']' timed out after 1200.0 seconds</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V72" s="2" t="n"/>
+      <c r="W72" s="2" t="n"/>
+      <c r="X72" s="2" t="n"/>
+      <c r="Y72" s="2" t="n"/>
+      <c r="Z72" s="2" t="n"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\react-performance-debugging\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>reserves-at-risk-calc</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n">
+        <v>601.9059999999999</v>
+      </c>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:04455a0338c84a104ced', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\reserves-at-risk-calc\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V73" s="2" t="n"/>
+      <c r="W73" s="2" t="n"/>
+      <c r="X73" s="2" t="n"/>
+      <c r="Y73" s="2" t="n"/>
+      <c r="Z73" s="2" t="n"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\reserves-at-risk-calc\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>sales-pivot-analysis</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>TASK_FAILED</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>session-4e51a62e-4c9a-4307-b094-96bf5123382e</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>600.813</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>413.329</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>448039</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>16141</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>pdf; xlsx</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>pdf; xlsx</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>test_outputs.py::TestPivotTableConfiguration::test_pivot_row_is_state; test_outputs.py::TestPivotTableConfiguration::test_pivot_uses_correct_aggregation; test_outputs.py::TestSourceDataContent::test_state_values_are_valid; test_outputs.py::TestDataTransformationCorrectness::test_pivot_cache_has_fields</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="n"/>
+      <c r="U74" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V74" s="2" t="n"/>
+      <c r="W74" s="2" t="n"/>
+      <c r="X74" s="2" t="n"/>
+      <c r="Y74" s="2" t="n"/>
+      <c r="Z74" s="2" t="n"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\sales-pivot-analysis\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>sec-financial-report</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="n"/>
+      <c r="I75" s="2" t="n">
+        <v>600.968</v>
+      </c>
+      <c r="J75" s="2" t="n"/>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="2" t="n"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:db6c1e3425e48d1ab8d1', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\sec-financial-report\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V75" s="2" t="n"/>
+      <c r="W75" s="2" t="n"/>
+      <c r="X75" s="2" t="n"/>
+      <c r="Y75" s="2" t="n"/>
+      <c r="Z75" s="2" t="n"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\sec-financial-report\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>seismic-phase-picking</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="n"/>
+      <c r="I76" s="2" t="n">
+        <v>1402.156</v>
+      </c>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="2" t="n"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:26e650c9aa2659152a46', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\seismic-phase-picking\\environment']' timed out after 900.0 seconds</t>
+        </is>
+      </c>
+      <c r="U76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V76" s="2" t="n"/>
+      <c r="W76" s="2" t="n"/>
+      <c r="X76" s="2" t="n"/>
+      <c r="Y76" s="2" t="n"/>
+      <c r="Z76" s="2" t="n"/>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\seismic-phase-picking\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>setup-fuzzing-py</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>TIMEOUT</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>session-7d8fe2a3-2c0d-4371-95b0-bb12d56e1316</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>4698.438</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1800.515</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>1645428</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>62764</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>discover-important-function; fuzzing-python; setup-env</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>test_setup.py::test_discovery</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="n"/>
+      <c r="U77" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V77" s="2" t="n"/>
+      <c r="W77" s="2" t="n"/>
+      <c r="X77" s="2" t="n"/>
+      <c r="Y77" s="2" t="n"/>
+      <c r="Z77" s="2" t="n"/>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\setup-fuzzing-py\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>shock-analysis-demand</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="n"/>
+      <c r="I78" s="2" t="n">
+        <v>6610.75</v>
+      </c>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="2" t="n"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:2cd84b4898a3cf148f01', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\shock-analysis-demand\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V78" s="2" t="n"/>
+      <c r="W78" s="2" t="n"/>
+      <c r="X78" s="2" t="n"/>
+      <c r="Y78" s="2" t="n"/>
+      <c r="Z78" s="2" t="n"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\shock-analysis-demand\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>shock-analysis-supply</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2" t="n"/>
+      <c r="I79" s="2" t="n">
+        <v>6004.281</v>
+      </c>
+      <c r="J79" s="2" t="n"/>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="2" t="n"/>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr"/>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: buntu noble-backports/universe amd64 Packages [31.0 kB]
+#6 212.7 Get:5 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages [15.0 MB]
+#6 218.8 Ign:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 223.8 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 228.8 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 233.9 Ign:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 238.9 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 244.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 249.0 Err:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+#6 249.0   502  Bad Gateway [IP: 91.189.92.23 80]
+#6 254.0 Err:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 254.0   502  Bad Gateway [IP: 91.189.92.23 80]
+#6 259.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+#6 259.0 Reading package lists...
+#6 259.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+#6 259.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/5] RUN apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+238.9 Ign:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+244.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+249.0 Err:6 http://archive.ubuntu.com/ubuntu noble/restricted amd64 Packages
+249.0   502  Bad Gateway [IP: 91.189.92.23 80]
+254.0 Err:9 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+254.0   502  Bad Gateway [IP: 91.189.92.23 80]
+259.0 Ign:12 http://archive.ubuntu.com/ubuntu noble-updates/multiverse amd64 Packages
+259.0 Reading package lists...
+259.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+259.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Python, pip, LibreOffice for Excel formula evaluation
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     python3 \
+   8 | &gt;&gt;&gt;     python3-pip \
+   9 | &gt;&gt;&gt;     python3-venv \
+  10 | &gt;&gt;&gt;     libreoffice \
+  11 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  12 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     python3     python3-pip     python3-venv     libreoffice     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V79" s="2" t="n"/>
+      <c r="W79" s="2" t="n"/>
+      <c r="X79" s="2" t="n"/>
+      <c r="Y79" s="2" t="n"/>
+      <c r="Z79" s="2" t="n"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\shock-analysis-supply\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>simpo-code-reproduction</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>TASK_FAILED</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>session-499d97ce-ef84-41d1-ae65-19097119b673</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1544.578</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>1323.781</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1657073</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>40062</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment; pdf</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment; pdf</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>nlp-research-repo-package-installment</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="n"/>
+      <c r="U80" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V80" s="2" t="n"/>
+      <c r="W80" s="2" t="n"/>
+      <c r="X80" s="2" t="n"/>
+      <c r="Y80" s="2" t="n"/>
+      <c r="Z80" s="2" t="n"/>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\simpo-code-reproduction\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>software-dependency-audit</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n">
+        <v>861.907</v>
+      </c>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n"/>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="inlineStr"/>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: /debian trixie InRelease
+#6 5.316   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 7.991 Get:2 http://deb.debian.org/debian trixie-updates InRelease [47.3 kB]
+#6 13.00 Err:3 http://deb.debian.org/debian-security trixie-security InRelease
+#6 13.00   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 18.01 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 23.02 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 23.02   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 28.04 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 33.05 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+#6 33.05   502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.05 Reading package lists...
+#6 33.06 E: Failed to fetch http://deb.debian.org/debian/dists/trixie/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.06 E: The repository 'http://deb.debian.org/debian trixie InRelease' is no longer signed.
+#6 33.06 E: Failed to fetch http://deb.debian.org/debian-security/dists/trixie-security/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+#6 33.06 E: The repository 'http://deb.debian.org/debian-security trixie-security InRelease' is no longer signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+23.02 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+23.02   502  Bad Gateway [IP: 199.232.162.132 80]
+28.04 Ign:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+33.05 Err:4 http://deb.debian.org/debian trixie-updates/main amd64 Packages
+33.05   502  Bad Gateway [IP: 199.232.162.132 80]
+33.05 Reading package lists...
+33.06 E: Failed to fetch http://deb.debian.org/debian/dists/trixie/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+33.06 E: The repository 'http://deb.debian.org/debian trixie InRelease' is no longer signed.
+33.06 E: Failed to fetch http://deb.debian.org/debian-security/dists/trixie-security/InRelease  502  Bad Gateway [IP: 199.232.162.132 80]
+33.06 E: The repository 'http://deb.debian.org/debian-security trixie-security InRelease' is no longer signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install dependencies
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     wget \
+   9 | &gt;&gt;&gt;     gnupg2 \
+  10 | &gt;&gt;&gt;     lsb-release \
+  11 | &gt;&gt;&gt;     git \
+  12 | &gt;&gt;&gt;     unzip \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     gnupg2     lsb-release     git     unzip     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V81" s="2" t="n"/>
+      <c r="W81" s="2" t="n"/>
+      <c r="X81" s="2" t="n"/>
+      <c r="Y81" s="2" t="n"/>
+      <c r="Z81" s="2" t="n"/>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\software-dependency-audit\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>spring-boot-jakarta-migration</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="n"/>
+      <c r="I82" s="2" t="n">
+        <v>1085.578</v>
+      </c>
+      <c r="J82" s="2" t="n"/>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="2" t="n"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="2" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: ges [117 kB]
+#6 160.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 167.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 172.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 172.9   Connection failed [IP: 91.189.92.23 80]
+#6 177.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 182.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 182.9   Connection failed [IP: 91.189.92.23 80]
+#6 187.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 193.0 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 193.0   Connection failed [IP: 91.189.92.23 80]
+#6 193.0 Reading package lists...
+#6 193.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+#6 193.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+#6 193.0 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.92.23 80]
+#6 193.0 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [ 2/11] RUN apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+182.9 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+182.9   Connection failed [IP: 91.189.92.23 80]
+187.9 Ign:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+193.0 Err:8 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+193.0   Connection failed [IP: 91.189.92.23 80]
+193.0 Reading package lists...
+193.0 E: Failed to fetch http://security.ubuntu.com/ubuntu/dists/noble-security/InRelease  502  Bad Gateway [IP: 185.125.190.81 80]
+193.0 E: The repository 'http://security.ubuntu.com/ubuntu noble-security InRelease' is not signed.
+193.0 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.92.23 80]
+193.0 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+------
+Dockerfile:10
+--------------------
+   9 |     # Install essential packages
+  10 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+  11 | &gt;&gt;&gt;     curl \
+  12 | &gt;&gt;&gt;     wget \
+  13 | &gt;&gt;&gt;     git \
+  14 | &gt;&gt;&gt;     unzip \
+  15 | &gt;&gt;&gt;     zip \
+  16 | &gt;&gt;&gt;     vim \
+  17 | &gt;&gt;&gt;     nano \
+  18 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  19 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     wget     git     unzip     zip     vim     nano     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V82" s="2" t="n"/>
+      <c r="W82" s="2" t="n"/>
+      <c r="X82" s="2" t="n"/>
+      <c r="Y82" s="2" t="n"/>
+      <c r="Z82" s="2" t="n"/>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\spring-boot-jakarta-migration\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>suricata-custom-exfil</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="n"/>
+      <c r="I83" s="2" t="n">
+        <v>513.75</v>
+      </c>
+      <c r="J83" s="2" t="n"/>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="2" t="n"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: #0 building with "desktop-linux" instance using docker driver
+#1 [internal] load build definition from Dockerfile
+#1 transferring dockerfile: 2.45kB done
+#1 DONE 0.0s
+#2 [internal] load metadata for docker.io/jasonish/suricata:7.0.11
+#2 ERROR: failed to do request: Head "https://registry-1.docker.io/v2/jasonish/suricata/manifests/7.0.11": EOF
+------
+ &gt; [internal] load metadata for docker.io/jasonish/suricata:7.0.11:
+------
+Dockerfile:1
+--------------------
+   1 | &gt;&gt;&gt; FROM jasonish/suricata:7.0.11
+   2 |     
+   3 |     ENV DEBIAN_FRONTEND=noninteractive
+--------------------
+ERROR: failed to build: failed to solve: jasonish/suricata:7.0.11: failed to resolve source metadata for docker.io/jasonish/suricata:7.0.11: failed to do request: Head "https://registry-1.docker.io/v2/jasonish/suricata/manifests/7.0.11": EOF
+</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V83" s="2" t="n"/>
+      <c r="W83" s="2" t="n"/>
+      <c r="X83" s="2" t="n"/>
+      <c r="Y83" s="2" t="n"/>
+      <c r="Z83" s="2" t="n"/>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\suricata-custom-exfil\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>syzkaller-ppdev-syzlang</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>INTERRUPTED</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2" t="n"/>
+      <c r="I84" s="2" t="n">
+        <v>1396.984</v>
+      </c>
+      <c r="J84" s="2" t="n"/>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="2" t="n"/>
+      <c r="N84" s="2" t="n"/>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="n"/>
+      <c r="U84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V84" s="2" t="n"/>
+      <c r="W84" s="2" t="n"/>
+      <c r="X84" s="2" t="n"/>
+      <c r="Y84" s="2" t="n"/>
+      <c r="Z84" s="2" t="n"/>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\syzkaller-ppdev-syzlang\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>threejs-structure-parser</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2" t="n"/>
+      <c r="I85" s="2" t="n">
+        <v>296.812</v>
+      </c>
+      <c r="J85" s="2" t="n"/>
+      <c r="K85" s="2" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="2" t="n"/>
+      <c r="N85" s="2" t="n"/>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: gn:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+#6 72.77 Err:7 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+#6 72.77   502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.00 Err:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+#6 76.00   502  Bad Gateway [IP: 91.189.92.24 80]
+#6 76.01 Reading package lists...
+#6 76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble InRelease' is not signed.
+#6 76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+70.99 Ign:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+72.77 Err:7 http://archive.ubuntu.com/ubuntu noble-updates/main amd64 Packages
+72.77   502  Bad Gateway [IP: 91.189.91.82 80]
+76.00 Err:9 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages
+76.00   502  Bad Gateway [IP: 91.189.92.24 80]
+76.01 Reading package lists...
+76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble InRelease' is not signed.
+76.01 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+76.01 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Node.js, npm, and Python
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     python3 \
+   9 | &gt;&gt;&gt;     python3-pip \
+  10 | &gt;&gt;&gt;     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash - \
+  11 | &gt;&gt;&gt;     &amp;&amp; apt-get install -y nodejs \
+  12 | &gt;&gt;&gt;     &amp;&amp; apt-get clean \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="n"/>
+      <c r="W85" s="2" t="n"/>
+      <c r="X85" s="2" t="n"/>
+      <c r="Y85" s="2" t="n"/>
+      <c r="Z85" s="2" t="n"/>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\threejs-structure-parser\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>threejs-to-obj</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="2" t="n"/>
+      <c r="I86" s="2" t="n">
+        <v>178.062</v>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="2" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="2" t="n"/>
+      <c r="N86" s="2" t="n"/>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docker exited 1: ntu.com/ubuntu noble/universe amd64 Packages
+#6 73.58 Get:3 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages [45.4 kB]
+#6 74.13 Err:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+#6 74.13   502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.14 Reading package lists...
+#6 74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+#6 74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+#6 74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+#6 ERROR: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+------
+ &gt; [2/6] RUN apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*:
+68.10 Get:5 http://security.ubuntu.com/ubuntu noble-security/restricted amd64 Packages [1713 kB]
+69.11 Ign:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+73.58 Get:3 http://security.ubuntu.com/ubuntu noble-security/multiverse amd64 Packages [45.4 kB]
+74.13 Err:12 http://archive.ubuntu.com/ubuntu noble/universe amd64 Packages
+74.13   502  Bad Gateway [IP: 91.189.91.82 80]
+74.14 Reading package lists...
+74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-updates/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-updates InRelease' is not signed.
+74.23 E: Failed to fetch http://archive.ubuntu.com/ubuntu/dists/noble-backports/InRelease  502  Bad Gateway [IP: 91.189.91.82 80]
+74.23 E: The repository 'http://archive.ubuntu.com/ubuntu noble-backports InRelease' is not signed.
+------
+Dockerfile:6
+--------------------
+   5 |     # Install Node.js, npm, and Python
+   6 | &gt;&gt;&gt; RUN apt-get update &amp;&amp; apt-get install -y \
+   7 | &gt;&gt;&gt;     curl \
+   8 | &gt;&gt;&gt;     python3 \
+   9 | &gt;&gt;&gt;     python3-pip \
+  10 | &gt;&gt;&gt;     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash - \
+  11 | &gt;&gt;&gt;     &amp;&amp; apt-get install -y nodejs \
+  12 | &gt;&gt;&gt;     &amp;&amp; apt-get clean \
+  13 | &gt;&gt;&gt;     &amp;&amp; rm -rf /var/lib/apt/lists/*
+  14 |     
+--------------------
+ERROR: failed to build: failed to solve: process "/bin/sh -c apt-get update &amp;&amp; apt-get install -y     curl     python3     python3-pip     &amp;&amp; curl -fsSL https://deb.nodesource.com/setup_20.x | bash -     &amp;&amp; apt-get install -y nodejs     &amp;&amp; apt-get clean     &amp;&amp; rm -rf /var/lib/apt/lists/*" did not complete successfully: exit code: 100
+</t>
+        </is>
+      </c>
+      <c r="U86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V86" s="2" t="n"/>
+      <c r="W86" s="2" t="n"/>
+      <c r="X86" s="2" t="n"/>
+      <c r="Y86" s="2" t="n"/>
+      <c r="Z86" s="2" t="n"/>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\threejs-to-obj\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>tictoc-unnecessary-abort-detection</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>INTERRUPTED</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n">
+        <v>918.953</v>
+      </c>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n"/>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>transaction-concurrency-control-foundations; transaction-protocol-reasoning; transaction-trace-analysis</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>Stop requested</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V87" s="2" t="n"/>
+      <c r="W87" s="2" t="n"/>
+      <c r="X87" s="2" t="n"/>
+      <c r="Y87" s="2" t="n"/>
+      <c r="Z87" s="2" t="n"/>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\tictoc-unnecessary-abort-detection\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>travel-planning</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>INTERRUPTED</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n">
+        <v>842.812</v>
+      </c>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>search-accommodations; search-attractions; search-cities; search-driving-distance; search-flights; search-restaurants</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>Stop requested</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V88" s="2" t="n"/>
+      <c r="W88" s="2" t="n"/>
+      <c r="X88" s="2" t="n"/>
+      <c r="Y88" s="2" t="n"/>
+      <c r="Z88" s="2" t="n"/>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\travel-planning\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>video-silence-remover</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ENVIRONMENT_ERROR</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>f17d59ed60bb55878db65750eee6cc591efe52c97351fb2c1ed850f9ff6b75a5</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n">
+        <v>763.078</v>
+      </c>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="inlineStr"/>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>Command '['docker', 'build', '-t', 'nextagent-bench/environment:61ba44051c2945cb6276', 'C:\\Project\\nextagent-bench\\datasets\\c44fb04745607db4d1c0b07a945ec3fbdfaa2bd955ae172667aaa7edc95b4ae2\\tasks\\video-silence-remover\\environment']' timed out after 600.0 seconds</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="n"/>
+      <c r="W89" s="2" t="n"/>
+      <c r="X89" s="2" t="n"/>
+      <c r="Y89" s="2" t="n"/>
+      <c r="Z89" s="2" t="n"/>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>C:\Project\nextagent-bench\runs\20261025-195147-f17d59ed-c79fa2\tasks\video-silence-remover\attempt-001</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>351d10db82ae26ed682cbe21f4a410506bc2b8d9a0c03c5d1fdba0892ddc03f5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC62"/>
+  <autoFilter ref="A1:AC89"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>